--- a/output_file.xlsx
+++ b/output_file.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Result</t>
         </is>
       </c>
     </row>
